--- a/public/exports-60-250-with-coowners/29189730.xlsx
+++ b/public/exports-60-250-with-coowners/29189730.xlsx
@@ -5239,7 +5239,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t xml:space="preserve">311654760</t>
+          <t xml:space="preserve">311654759</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M88" t="inlineStr">
@@ -6664,12 +6664,12 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M90" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706452</t>
+          <t xml:space="preserve">311706451</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t xml:space="preserve">OBH Ingeniørservice A/S</t>
+          <t xml:space="preserve"/>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706979</t>
+          <t xml:space="preserve">311706728</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -7489,7 +7489,7 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706979</t>
+          <t xml:space="preserve">311706728</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706979</t>
+          <t xml:space="preserve">311706728</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706982</t>
+          <t xml:space="preserve">311706895</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706982</t>
+          <t xml:space="preserve">311706895</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t xml:space="preserve">311706968</t>
+          <t xml:space="preserve">311706709</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
